--- a/outputs_xlsx_solution/test_1.4-wide-NC-1.xlsx
+++ b/outputs_xlsx_solution/test_1.4-wide-NC-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
   </si>
   <si>
@@ -147,6 +150,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -588,7 +594,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -608,13 +614,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -634,16 +640,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -663,16 +669,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -692,16 +698,16 @@
         <v>9</v>
       </c>
       <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -730,7 +736,7 @@
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -750,7 +756,7 @@
         <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -762,7 +768,7 @@
         <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -794,10 +800,10 @@
         <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -808,7 +814,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -817,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
@@ -829,7 +835,7 @@
         <v>14</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -840,7 +846,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -867,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -878,7 +884,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -887,16 +893,16 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
         <v>14</v>
       </c>
       <c r="M12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -907,7 +913,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -916,16 +922,16 @@
         <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
         <v>14</v>
       </c>
       <c r="N13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -936,7 +942,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -945,22 +951,22 @@
         <v>9</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
         <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -971,7 +977,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -980,19 +986,19 @@
         <v>9</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15" t="s">
         <v>14</v>
       </c>
       <c r="P15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1003,7 +1009,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1012,24 +1018,24 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P16" t="s">
         <v>14</v>
       </c>
       <c r="Q16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1037,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1045,15 +1051,15 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1061,39 +1067,55 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
         <v>36</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
         <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
